--- a/feature-cb-ibd-ig/StructureDefinition-SIMAlgemeneMeting.xlsx
+++ b/feature-cb-ibd-ig/StructureDefinition-SIMAlgemeneMeting.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T14:27:57+00:00</t>
+    <t>2026-10-26T15:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-cb-ibd-ig/StructureDefinition-SIMAlgemeneMeting.xlsx
+++ b/feature-cb-ibd-ig/StructureDefinition-SIMAlgemeneMeting.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="248">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T15:58:19+00:00</t>
+    <t>2026-10-29T22:11:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Logisch model voor een algemeneMeting binnen het Santeon Informatiemodel.</t>
+    <t>Generiek logisch model voor een algemene meting binnen het Santeon Informatiemodel.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -231,10 +231,10 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: SIM CSVs</t>
-  </si>
-  <si>
-    <t>Mapping: FHIR</t>
+    <t>Mapping: SIM CSV</t>
+  </si>
+  <si>
+    <t>Mapping: SIMAlgemeneMeting naar FHIR</t>
   </si>
   <si>
     <t/>
@@ -253,10 +253,38 @@
     <t>Base</t>
   </si>
   <si>
+    <t>SIMAlgemeneMeting.MetingID</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Uniek ID (key) binnen patiënt per meting</t>
+  </si>
+  <si>
+    <t>AlgemeneMeting;MetingID</t>
+  </si>
+  <si>
+    <t>Observation.identifier</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.PatientIdentificatienummer</t>
+  </si>
+  <si>
+    <t>Identificatienummer van de patiënt</t>
+  </si>
+  <si>
+    <t>AlgemeneMeting;Identificatienummer</t>
+  </si>
+  <si>
+    <t>Observation.subject</t>
+  </si>
+  <si>
     <t>SIMAlgemeneMeting.MetingNaam</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -272,8 +300,8 @@
     <t>https://ig.santeon.nl/sim-on-fhir/ValueSet/Santeon-MetingNaamCodelijst</t>
   </si>
   <si>
-    <t>validatie-metingnaam-uitslagcode:Valideert de relatie tussen MetingNaam en het bijbehorende type uitslag. Voor metingen met een gecodeerde uitslag moet UitslagCode afkomstig zijn uit de ValueSet die aan de betreffende MetingNaam is gekoppeld. Bijvoorbeeld: wanneer MetingNaam alcoholgebruik is (SNOMED CT 228273003), moet UitslagCode afkomstig zijn uit AlcoholGebruikStatusCodelijst. Dit geldt voor alle vastgelegde [MetingNaam-UitslagCode](&lt;a href='https://dev.azure.com/SanteonNL/Santeon/_git/HipsETL?path=/SIM/informatiemodel%20Santeon%20valueSets%20relation.csv&lt;/a&gt;)-combinaties. Metingen die niet in deze combinaties zijn vastgelegd, maar wel voorkomen in Santeon_MetingNaamCodelijst, hebben een UitslagWaarde als uitkomst. {(MetingNaam.coding.where(system = 'http://snomed.info/sct' and code = '228273003').exists() implies UitslagCode.memberOf('https://ig.santeon.nl/sim-on-fhir/ValueSet/AlcoholGebruikStatusCodelijst')) or (MetingNaam.coding.where(system = 'http://loinc.org' and code = '38445-3').exists() implies UitslagWaarde.exists())}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -357,26 +385,22 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>SIMAlgemeneMeting.MetingNaam.coding.system</t>
   </si>
   <si>
-    <t>MetingNaamCodeSysteem</t>
+    <t>AlgemeneMeting;MetingNaamCodeSysteem</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.MetingNaam.coding.code</t>
   </si>
   <si>
-    <t>MetingNaamCode</t>
+    <t>AlgemeneMeting;MetingNaamCode</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.MetingNaam.coding.display</t>
   </si>
   <si>
-    <t>MetingNaamOmschrijving</t>
+    <t>AlgemeneMeting;MetingNaamOmschrijving</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.MetingNaam.text</t>
@@ -407,7 +431,7 @@
     <t>Datum en eventueel tijd die het dichtst ligt bij het daadwerkelijke meetmoment of de observatie</t>
   </si>
   <si>
-    <t>MetingDatumTijd</t>
+    <t>AlgemeneMeting;MetingDatumTijd</t>
   </si>
   <si>
     <t>Observation.effectiveDateTime</t>
@@ -420,11 +444,11 @@
 </t>
   </si>
   <si>
-    <t>Numerieke uitslag van de meting, met eenheid (UCUM) en eventueel een vergelijkingsoperator (&lt;, &lt;=, &gt;=, &gt;)</t>
-  </si>
-  <si>
-    <t>validatie-metingnaam-uitslagcode:Valideert de relatie tussen MetingNaam en het bijbehorende type uitslag. Voor metingen met een gecodeerde uitslag moet UitslagCode afkomstig zijn uit de ValueSet die aan de betreffende MetingNaam is gekoppeld. Bijvoorbeeld: wanneer MetingNaam alcoholgebruik is (SNOMED CT 228273003), moet UitslagCode afkomstig zijn uit AlcoholGebruikStatusCodelijst. Dit geldt voor alle vastgelegde [MetingNaam-UitslagCode](&lt;a href='https://dev.azure.com/SanteonNL/Santeon/_git/HipsETL?path=/SIM/informatiemodel%20Santeon%20valueSets%20relation.csv&lt;/a&gt;)-combinaties. Metingen die niet in deze combinaties zijn vastgelegd, maar wel voorkomen in Santeon_MetingNaamCodelijst, hebben een UitslagWaarde als uitkomst. {(MetingNaam.coding.where(system = 'http://snomed.info/sct' and code = '228273003').exists() implies UitslagCode.memberOf('https://ig.santeon.nl/sim-on-fhir/ValueSet/AlcoholGebruikStatusCodelijst')) or (MetingNaam.coding.where(system = 'http://loinc.org' and code = '38445-3').exists() implies UitslagWaarde.exists())}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+    <t>Numerieke uitslag van de meting, met eenheid (UCUM) en eventueel een vergelijkingsoperator</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
   </si>
   <si>
     <t>Observation.valueQuantity</t>
@@ -458,7 +482,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>UitslagWaarde</t>
+    <t>AlgemeneMeting;UitslagWaarde</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagWaarde.comparator</t>
@@ -489,7 +513,7 @@
     <t>Quantity.comparator</t>
   </si>
   <si>
-    <t>UitslagWaardeOperator</t>
+    <t>AlgemeneMeting;UitslagWaardeOperator</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagWaarde.unit</t>
@@ -530,7 +554,7 @@
 </t>
   </si>
   <si>
-    <t>UitslagWaardeEenheidSysteem</t>
+    <t>AlgemeneMeting;UitslagWaardeEenheidSysteem</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagWaarde.code</t>
@@ -551,7 +575,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>UitslagWaardeEenheid</t>
+    <t>AlgemeneMeting;UitslagWaardeEenheid</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik</t>
@@ -603,25 +627,25 @@
     <t>SIMAlgemeneMeting.UitslagBereik.low.value</t>
   </si>
   <si>
-    <t>ObservationValueRangeLow</t>
+    <t>AlgemeneMeting;ObservationValueRangeLow</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.low.unit</t>
   </si>
   <si>
-    <t>ObservationValueRangeLowUnit</t>
+    <t>AlgemeneMeting;ObservationValueRangeLowUnit</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.low.system</t>
   </si>
   <si>
-    <t>ObservationValueRangeLowSystem</t>
+    <t>AlgemeneMeting;ObservationValueRangeLowSystem</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.low.code</t>
   </si>
   <si>
-    <t>ObservationValueRangeLowCode</t>
+    <t>AlgemeneMeting;ObservationValueRangeLowCode</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.high</t>
@@ -642,25 +666,25 @@
     <t>SIMAlgemeneMeting.UitslagBereik.high.value</t>
   </si>
   <si>
-    <t>ObservationValueRangeHigh</t>
+    <t>AlgemeneMeting;ObservationValueRangeHigh</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.high.unit</t>
   </si>
   <si>
-    <t>ObservationValueRangeHighUnit</t>
+    <t>AlgemeneMeting;ObservationValueRangeHighUnit</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.high.system</t>
   </si>
   <si>
-    <t>ObservationValueRangeHighSystem</t>
+    <t>AlgemeneMeting;ObservationValueRangeHighSystem</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagBereik.high.code</t>
   </si>
   <si>
-    <t>ObservationValueRangeHighCode</t>
+    <t>AlgemeneMeting;ObservationValueRangeHighCode</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagCode</t>
@@ -669,7 +693,7 @@
     <t>Gecodeerde uitslag van de meting</t>
   </si>
   <si>
-    <t>Welke ValueSet van toepassing is op UitslagCode wordt bepaald door MetingNaam, zie invariants.</t>
+    <t>Welke ValueSet van toepassing is op UitslagCode wordt bepaald door MetingNaam. De bijbehorende terminologierelaties worden afzonderlijk beheerd.</t>
   </si>
   <si>
     <t>Observation.valueCodeableConcept</t>
@@ -687,19 +711,19 @@
     <t>SIMAlgemeneMeting.UitslagCode.coding.system</t>
   </si>
   <si>
-    <t>UitslagCodeSysteem</t>
+    <t>AlgemeneMeting;UitslagCodeSysteem</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagCode.coding.code</t>
   </si>
   <si>
-    <t>UitslagCode</t>
+    <t>AlgemeneMeting;UitslagCode</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagCode.coding.display</t>
   </si>
   <si>
-    <t>UitslagCodeOmschrijving</t>
+    <t>AlgemeneMeting;UitslagCodeOmschrijving</t>
   </si>
   <si>
     <t>SIMAlgemeneMeting.UitslagCode.text</t>
@@ -711,10 +735,49 @@
     <t>Datum en eventueel tijd als antwoord op een vraag, bijvoorbeeld: sinds wanneer rookt u? Een vage datumtijd (alleen jaar of datum) is niet wenselijk maar wel toegestaan.</t>
   </si>
   <si>
-    <t>UitslagDatumTijd</t>
+    <t>AlgemeneMeting;UitslagDatumTijd</t>
   </si>
   <si>
     <t>Observation.valueDateTime</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode</t>
+  </si>
+  <si>
+    <t>Methode waarmee de meting is uitgevoerd</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.id</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.extension</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.coding</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.coding.system</t>
+  </si>
+  <si>
+    <t>AlgemeneMeting;MeetmethodeCodeSysteem</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.coding.code</t>
+  </si>
+  <si>
+    <t>AlgemeneMeting;MeetmethodeCode</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.coding.display</t>
+  </si>
+  <si>
+    <t>AlgemeneMeting;MeetmethodeOmschrijving</t>
+  </si>
+  <si>
+    <t>SIMAlgemeneMeting.Meetmethode.text</t>
   </si>
 </sst>
 </file>
@@ -1016,11 +1079,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL41"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.45703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.45703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.3984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.3984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1050,12 +1113,12 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.45703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.39453125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="29.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="43.23046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="37.42578125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1341,11 +1404,13 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y3" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y3" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z3" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1375,21 +1440,21 @@
         <v>74</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1397,7 +1462,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>80</v>
@@ -1412,13 +1477,13 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1469,10 +1534,10 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>80</v>
@@ -1484,29 +1549,29 @@
         <v>74</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>74</v>
@@ -1518,17 +1583,15 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>74</v>
@@ -1553,57 +1616,55 @@
         <v>74</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="Y5" s="2"/>
       <c r="Z5" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1614,7 +1675,7 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1623,23 +1684,19 @@
         <v>74</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>74</v>
       </c>
@@ -1687,19 +1744,19 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>74</v>
@@ -1710,20 +1767,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
       </c>
@@ -1734,11 +1793,17 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>74</v>
@@ -1775,32 +1840,34 @@
         <v>74</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH7" s="2"/>
+      <c r="AH7" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>74</v>
@@ -1808,10 +1875,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1821,7 +1888,9 @@
       <c r="F8" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
       </c>
@@ -1829,15 +1898,23 @@
         <v>74</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O8" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="P8" t="s" s="2">
         <v>74</v>
       </c>
@@ -1885,20 +1962,22 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH8" s="2"/>
+      <c r="AH8" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>74</v>
@@ -1906,10 +1985,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1983,7 +2062,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1996,7 +2075,7 @@
         <v>74</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>74</v>
@@ -2004,10 +2083,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2017,9 +2096,7 @@
       <c r="F10" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G10" s="2"/>
       <c r="H10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2027,23 +2104,15 @@
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
       </c>
@@ -2091,22 +2160,20 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH10" s="2"/>
+      <c r="AI10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK10" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ10" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AK10" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>74</v>
@@ -2127,9 +2194,7 @@
       <c r="F11" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G11" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2140,14 +2205,10 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2202,9 +2263,7 @@
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH11" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH11" s="2"/>
       <c r="AI11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2212,18 +2271,18 @@
         <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2243,19 +2302,23 @@
         <v>74</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2303,7 +2366,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2315,21 +2378,21 @@
         <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2352,13 +2415,13 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2409,7 +2472,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2424,29 +2487,29 @@
         <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>74</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -2458,17 +2521,15 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
@@ -2505,45 +2566,45 @@
         <v>74</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2563,23 +2624,19 @@
         <v>74</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2627,7 +2684,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2639,10 +2696,10 @@
         <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -2650,50 +2707,48 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="J16" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>146</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q16" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2713,37 +2768,37 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>74</v>
@@ -2752,7 +2807,7 @@
         <v>111</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>74</v>
@@ -2760,10 +2815,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2783,20 +2838,22 @@
         <v>74</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O17" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -2845,7 +2902,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2857,10 +2914,10 @@
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>74</v>
@@ -2868,10 +2925,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2888,28 +2945,30 @@
         <v>74</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q18" s="2"/>
+      <c r="Q18" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="R18" t="s" s="2">
         <v>74</v>
       </c>
@@ -2929,13 +2988,13 @@
         <v>74</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>74</v>
@@ -2953,7 +3012,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2962,13 +3021,13 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>74</v>
@@ -2976,10 +3035,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2999,22 +3058,20 @@
         <v>74</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
@@ -3063,7 +3120,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3075,10 +3132,10 @@
         <v>74</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>74</v>
@@ -3086,10 +3143,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3109,19 +3166,21 @@
         <v>74</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>74</v>
       </c>
@@ -3169,7 +3228,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3178,24 +3237,24 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3215,19 +3274,23 @@
         <v>74</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>74</v>
       </c>
@@ -3275,7 +3338,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3287,10 +3350,10 @@
         <v>74</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
@@ -3298,21 +3361,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3324,17 +3387,15 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -3371,45 +3432,45 @@
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3429,20 +3490,18 @@
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>182</v>
+        <v>97</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>74</v>
@@ -3491,7 +3550,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3503,7 +3562,7 @@
         <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>74</v>
@@ -3521,13 +3580,15 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G24" s="2"/>
+      <c r="G24" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
       </c>
@@ -3538,11 +3599,17 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>74</v>
@@ -3579,32 +3646,34 @@
         <v>74</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH24" s="2"/>
+      <c r="AH24" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
@@ -3612,10 +3681,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3625,7 +3694,9 @@
       <c r="F25" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
       </c>
@@ -3633,14 +3704,20 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -3689,20 +3766,22 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH25" s="2"/>
+      <c r="AH25" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -3710,10 +3789,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3787,7 +3866,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3800,7 +3879,7 @@
         <v>74</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>74</v>
@@ -3808,10 +3887,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3885,7 +3964,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3898,7 +3977,7 @@
         <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>74</v>
@@ -3906,10 +3985,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3919,9 +3998,7 @@
       <c r="F28" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G28" s="2"/>
       <c r="H28" t="s" s="2">
         <v>74</v>
       </c>
@@ -3929,20 +4006,14 @@
         <v>74</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>74</v>
@@ -3996,17 +4067,15 @@
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH28" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH28" s="2"/>
       <c r="AI28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>74</v>
+        <v>201</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>74</v>
@@ -4014,10 +4083,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4091,7 +4160,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4104,7 +4173,7 @@
         <v>74</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>74</v>
@@ -4112,10 +4181,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4125,7 +4194,9 @@
       <c r="F30" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G30" s="2"/>
+      <c r="G30" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
       </c>
@@ -4133,14 +4204,20 @@
         <v>74</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
@@ -4189,20 +4266,22 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH30" s="2"/>
+      <c r="AH30" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>74</v>
@@ -4210,10 +4289,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4287,7 +4366,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4300,7 +4379,7 @@
         <v>74</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>74</v>
@@ -4308,10 +4387,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4385,7 +4464,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4398,7 +4477,7 @@
         <v>74</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>74</v>
@@ -4406,10 +4485,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4419,9 +4498,7 @@
       <c r="F33" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G33" s="2"/>
       <c r="H33" t="s" s="2">
         <v>74</v>
       </c>
@@ -4432,14 +4509,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4489,33 +4562,31 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH33" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH33" s="2"/>
       <c r="AI33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>212</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4525,9 +4596,7 @@
       <c r="F34" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G34" s="2"/>
       <c r="H34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4538,14 +4607,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>90</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4595,14 +4660,12 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>91</v>
+        <v>215</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH34" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH34" s="2"/>
       <c r="AI34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4610,7 +4673,7 @@
         <v>74</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>74</v>
+        <v>216</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>74</v>
@@ -4618,21 +4681,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4644,17 +4707,15 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -4691,45 +4752,45 @@
         <v>74</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>74</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4740,7 +4801,7 @@
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4749,23 +4810,19 @@
         <v>74</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -4813,19 +4870,19 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>74</v>
@@ -4836,20 +4893,22 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G37" s="2"/>
+      <c r="G37" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
       </c>
@@ -4860,11 +4919,17 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4901,32 +4966,34 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH37" s="2"/>
+      <c r="AH37" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>217</v>
+        <v>74</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>74</v>
@@ -4934,10 +5001,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4947,7 +5014,9 @@
       <c r="F38" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G38" s="2"/>
+      <c r="G38" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
       </c>
@@ -4955,15 +5024,23 @@
         <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5011,20 +5088,22 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH38" s="2"/>
+      <c r="AH38" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>74</v>
@@ -5032,10 +5111,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5109,7 +5188,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -5122,7 +5201,7 @@
         <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>74</v>
@@ -5130,10 +5209,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5143,9 +5222,7 @@
       <c r="F40" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G40" s="2"/>
       <c r="H40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5153,23 +5230,15 @@
         <v>74</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5217,22 +5286,20 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH40" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="AH40" s="2"/>
       <c r="AI40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>74</v>
@@ -5240,10 +5307,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5253,9 +5320,7 @@
       <c r="F41" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="G41" s="2"/>
       <c r="H41" t="s" s="2">
         <v>74</v>
       </c>
@@ -5266,14 +5331,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5323,25 +5384,1073 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH41" t="s" s="2">
+      <c r="AH41" s="2"/>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>226</v>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH48" s="2"/>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH49" s="2"/>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" s="2"/>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
